--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246702</v>
+        <v>121246864</v>
       </c>
       <c r="B3" t="n">
-        <v>91959</v>
+        <v>4772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529395</v>
+        <v>529301</v>
       </c>
       <c r="R3" t="n">
-        <v>6468217</v>
+        <v>6468100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246864</v>
+        <v>121246702</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>91959</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,28 +910,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529301</v>
+        <v>529395</v>
       </c>
       <c r="R4" t="n">
-        <v>6468100</v>
+        <v>6468217</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98842754</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246864</v>
+        <v>121246871</v>
       </c>
       <c r="B3" t="n">
         <v>4772</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529301</v>
+        <v>529291</v>
       </c>
       <c r="R3" t="n">
-        <v>6468100</v>
+        <v>6468142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246702</v>
+        <v>121246776</v>
       </c>
       <c r="B4" t="n">
-        <v>91959</v>
+        <v>4772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,26 +910,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529395</v>
+        <v>529371</v>
       </c>
       <c r="R4" t="n">
-        <v>6468217</v>
+        <v>6468131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247028</v>
+        <v>121246801</v>
       </c>
       <c r="B5" t="n">
-        <v>105176</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529549</v>
+        <v>529332</v>
       </c>
       <c r="R5" t="n">
-        <v>6468258</v>
+        <v>6468127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246744</v>
+        <v>121247028</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>105186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,32 +1129,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529315</v>
+        <v>529549</v>
       </c>
       <c r="R6" t="n">
-        <v>6468237</v>
+        <v>6468258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,12 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246776</v>
+        <v>121246702</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>91969</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,32 +1236,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529371</v>
+        <v>529395</v>
       </c>
       <c r="R7" t="n">
-        <v>6468131</v>
+        <v>6468217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246884</v>
+        <v>121246752</v>
       </c>
       <c r="B8" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,32 +1338,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529268</v>
+        <v>529338</v>
       </c>
       <c r="R8" t="n">
-        <v>6468138</v>
+        <v>6468183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246387</v>
+        <v>121246860</v>
       </c>
       <c r="B9" t="n">
-        <v>91965</v>
+        <v>4772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,38 +1445,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529285</v>
+        <v>529305</v>
       </c>
       <c r="R9" t="n">
-        <v>6468189</v>
+        <v>6468117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246852</v>
+        <v>121246734</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529325</v>
+        <v>529401</v>
       </c>
       <c r="R10" t="n">
-        <v>6468123</v>
+        <v>6468182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246866</v>
+        <v>121246744</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,31 +1660,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1704,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529289</v>
+        <v>529315</v>
       </c>
       <c r="R11" t="n">
-        <v>6468100</v>
+        <v>6468237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246857</v>
+        <v>121246884</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>4772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,31 +1772,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529305</v>
+        <v>529268</v>
       </c>
       <c r="R12" t="n">
-        <v>6468117</v>
+        <v>6468138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1868,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246871</v>
+        <v>121246864</v>
       </c>
       <c r="B13" t="n">
         <v>4772</v>
@@ -1919,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529291</v>
+        <v>529301</v>
       </c>
       <c r="R13" t="n">
-        <v>6468142</v>
+        <v>6468100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246860</v>
+        <v>121246857</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,32 +1988,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2090,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246752</v>
+        <v>121246852</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529338</v>
+        <v>529325</v>
       </c>
       <c r="R15" t="n">
-        <v>6468183</v>
+        <v>6468123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2190,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246700</v>
+        <v>121246891</v>
       </c>
       <c r="B16" t="n">
         <v>4772</v>
@@ -2234,11 +2227,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2246,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529395</v>
+        <v>529249</v>
       </c>
       <c r="R16" t="n">
-        <v>6468217</v>
+        <v>6468138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2309,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246742</v>
+        <v>121246387</v>
       </c>
       <c r="B17" t="n">
-        <v>91963</v>
+        <v>91975</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,29 +2310,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>788</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2352,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529315</v>
+        <v>529285</v>
       </c>
       <c r="R17" t="n">
-        <v>6468237</v>
+        <v>6468189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246719</v>
+        <v>121246866</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529388</v>
+        <v>529289</v>
       </c>
       <c r="R18" t="n">
-        <v>6468198</v>
+        <v>6468100</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246734</v>
+        <v>121246700</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,31 +2531,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529401</v>
+        <v>529395</v>
       </c>
       <c r="R19" t="n">
-        <v>6468182</v>
+        <v>6468217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246801</v>
+        <v>121246742</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>91973</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,31 +2643,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2673,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529332</v>
+        <v>529315</v>
       </c>
       <c r="R20" t="n">
-        <v>6468127</v>
+        <v>6468237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246891</v>
+        <v>121246719</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,32 +2749,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529249</v>
+        <v>529388</v>
       </c>
       <c r="R21" t="n">
-        <v>6468138</v>
+        <v>6468198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246387</v>
+        <v>121246866</v>
       </c>
       <c r="B17" t="n">
-        <v>91975</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,38 +2310,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2349,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529285</v>
+        <v>529289</v>
       </c>
       <c r="R17" t="n">
-        <v>6468189</v>
+        <v>6468100</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246866</v>
+        <v>121246387</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>91975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,31 +2417,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529289</v>
+        <v>529285</v>
       </c>
       <c r="R18" t="n">
-        <v>6468100</v>
+        <v>6468189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246700</v>
+        <v>121246742</v>
       </c>
       <c r="B19" t="n">
-        <v>4772</v>
+        <v>91973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,32 +2535,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2568,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529395</v>
+        <v>529315</v>
       </c>
       <c r="R19" t="n">
-        <v>6468217</v>
+        <v>6468237</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246742</v>
+        <v>121246719</v>
       </c>
       <c r="B20" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,30 +2637,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529315</v>
+        <v>529388</v>
       </c>
       <c r="R20" t="n">
-        <v>6468237</v>
+        <v>6468198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246719</v>
+        <v>121246700</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,31 +2744,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529388</v>
+        <v>529395</v>
       </c>
       <c r="R21" t="n">
-        <v>6468198</v>
+        <v>6468217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246742</v>
+        <v>121246700</v>
       </c>
       <c r="B19" t="n">
-        <v>91973</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,26 +2535,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2562,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529315</v>
+        <v>529395</v>
       </c>
       <c r="R19" t="n">
-        <v>6468237</v>
+        <v>6468217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246719</v>
+        <v>121246742</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,31 +2643,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2669,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529388</v>
+        <v>529315</v>
       </c>
       <c r="R20" t="n">
-        <v>6468198</v>
+        <v>6468237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246700</v>
+        <v>121246719</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,36 +2749,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529395</v>
+        <v>529388</v>
       </c>
       <c r="R21" t="n">
-        <v>6468217</v>
+        <v>6468198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246871</v>
+        <v>121246852</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,32 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529291</v>
+        <v>529325</v>
       </c>
       <c r="R3" t="n">
-        <v>6468142</v>
+        <v>6468123</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246776</v>
+        <v>121246857</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,36 +905,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529371</v>
+        <v>529305</v>
       </c>
       <c r="R4" t="n">
-        <v>6468131</v>
+        <v>6468117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1113,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247028</v>
+        <v>121246702</v>
       </c>
       <c r="B6" t="n">
-        <v>105186</v>
+        <v>91969</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,27 +1123,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529549</v>
+        <v>529395</v>
       </c>
       <c r="R6" t="n">
-        <v>6468258</v>
+        <v>6468217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,12 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246702</v>
+        <v>121246744</v>
       </c>
       <c r="B7" t="n">
-        <v>91969</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,26 +1229,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1263,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529395</v>
+        <v>529315</v>
       </c>
       <c r="R7" t="n">
-        <v>6468217</v>
+        <v>6468237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246752</v>
+        <v>121246871</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,31 +1337,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529338</v>
+        <v>529291</v>
       </c>
       <c r="R8" t="n">
-        <v>6468183</v>
+        <v>6468142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246860</v>
+        <v>121246864</v>
       </c>
       <c r="B9" t="n">
         <v>4772</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529305</v>
+        <v>529301</v>
       </c>
       <c r="R9" t="n">
-        <v>6468117</v>
+        <v>6468100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246734</v>
+        <v>121246742</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,31 +1553,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1585,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529401</v>
+        <v>529315</v>
       </c>
       <c r="R10" t="n">
-        <v>6468182</v>
+        <v>6468237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246744</v>
+        <v>121246734</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,36 +1659,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1697,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529315</v>
+        <v>529401</v>
       </c>
       <c r="R11" t="n">
-        <v>6468237</v>
+        <v>6468182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246884</v>
+        <v>121246719</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,32 +1766,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1805,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529268</v>
+        <v>529388</v>
       </c>
       <c r="R12" t="n">
-        <v>6468138</v>
+        <v>6468198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246864</v>
+        <v>121246776</v>
       </c>
       <c r="B13" t="n">
         <v>4772</v>
@@ -1905,7 +1898,11 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529301</v>
+        <v>529371</v>
       </c>
       <c r="R13" t="n">
-        <v>6468100</v>
+        <v>6468131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246857</v>
+        <v>121246752</v>
       </c>
       <c r="B14" t="n">
         <v>98081</v>
@@ -2020,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529305</v>
+        <v>529338</v>
       </c>
       <c r="R14" t="n">
-        <v>6468117</v>
+        <v>6468183</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246852</v>
+        <v>121246860</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,31 +2092,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529325</v>
+        <v>529305</v>
       </c>
       <c r="R15" t="n">
-        <v>6468123</v>
+        <v>6468117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246891</v>
+        <v>121246866</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,32 +2200,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529249</v>
+        <v>529289</v>
       </c>
       <c r="R16" t="n">
-        <v>6468138</v>
+        <v>6468100</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246866</v>
+        <v>121246387</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>91975</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,31 +2307,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2342,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529289</v>
+        <v>529285</v>
       </c>
       <c r="R17" t="n">
-        <v>6468100</v>
+        <v>6468189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246387</v>
+        <v>121246891</v>
       </c>
       <c r="B18" t="n">
-        <v>91975</v>
+        <v>4772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,38 +2421,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2456,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529285</v>
+        <v>529249</v>
       </c>
       <c r="R18" t="n">
-        <v>6468189</v>
+        <v>6468138</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246742</v>
+        <v>121246884</v>
       </c>
       <c r="B20" t="n">
-        <v>91973</v>
+        <v>4772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,26 +2645,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529315</v>
+        <v>529268</v>
       </c>
       <c r="R20" t="n">
-        <v>6468237</v>
+        <v>6468138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246719</v>
+        <v>121247028</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,25 +2749,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529388</v>
+        <v>529549</v>
       </c>
       <c r="R21" t="n">
-        <v>6468198</v>
+        <v>6468258</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98842754</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246852</v>
+        <v>121246860</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +798,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529325</v>
+        <v>529305</v>
       </c>
       <c r="R3" t="n">
-        <v>6468123</v>
+        <v>6468117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +897,7 @@
         <v>121246857</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1000,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246801</v>
+        <v>121246700</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,31 +1013,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529332</v>
+        <v>529395</v>
       </c>
       <c r="R5" t="n">
-        <v>6468127</v>
+        <v>6468217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1116,7 @@
         <v>121246702</v>
       </c>
       <c r="B6" t="n">
-        <v>91969</v>
+        <v>91981</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246744</v>
+        <v>121246734</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,36 +1231,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529315</v>
+        <v>529401</v>
       </c>
       <c r="R7" t="n">
-        <v>6468237</v>
+        <v>6468182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246871</v>
+        <v>121246801</v>
       </c>
       <c r="B8" t="n">
-        <v>4772</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,32 +1338,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529291</v>
+        <v>529332</v>
       </c>
       <c r="R8" t="n">
-        <v>6468142</v>
+        <v>6468127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246864</v>
+        <v>121246387</v>
       </c>
       <c r="B9" t="n">
-        <v>4772</v>
+        <v>91987</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,32 +1445,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529301</v>
+        <v>529285</v>
       </c>
       <c r="R9" t="n">
-        <v>6468100</v>
+        <v>6468189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246742</v>
+        <v>121246884</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>4772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,26 +1563,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1584,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529315</v>
+        <v>529268</v>
       </c>
       <c r="R10" t="n">
-        <v>6468237</v>
+        <v>6468138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246734</v>
+        <v>121246866</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529401</v>
+        <v>529289</v>
       </c>
       <c r="R11" t="n">
-        <v>6468182</v>
+        <v>6468100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246719</v>
+        <v>121246852</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529388</v>
+        <v>529325</v>
       </c>
       <c r="R12" t="n">
-        <v>6468198</v>
+        <v>6468123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246776</v>
+        <v>121246719</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,36 +1881,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529371</v>
+        <v>529388</v>
       </c>
       <c r="R13" t="n">
-        <v>6468131</v>
+        <v>6468198</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246752</v>
+        <v>121246742</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>91985</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,31 +1988,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2017,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529338</v>
+        <v>529315</v>
       </c>
       <c r="R14" t="n">
-        <v>6468183</v>
+        <v>6468237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246860</v>
+        <v>121246776</v>
       </c>
       <c r="B15" t="n">
         <v>4772</v>
@@ -2117,7 +2119,11 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2125,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529305</v>
+        <v>529371</v>
       </c>
       <c r="R15" t="n">
-        <v>6468117</v>
+        <v>6468131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246866</v>
+        <v>121246744</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,31 +2206,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2232,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529289</v>
+        <v>529315</v>
       </c>
       <c r="R16" t="n">
-        <v>6468100</v>
+        <v>6468237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246387</v>
+        <v>121246871</v>
       </c>
       <c r="B17" t="n">
-        <v>91975</v>
+        <v>4772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,38 +2318,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2346,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529285</v>
+        <v>529291</v>
       </c>
       <c r="R17" t="n">
-        <v>6468189</v>
+        <v>6468142</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246700</v>
+        <v>121247028</v>
       </c>
       <c r="B19" t="n">
-        <v>4772</v>
+        <v>105199</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,32 +2538,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529395</v>
+        <v>529549</v>
       </c>
       <c r="R19" t="n">
-        <v>6468217</v>
+        <v>6468258</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,7 +2629,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246884</v>
+        <v>121246864</v>
       </c>
       <c r="B20" t="n">
         <v>4772</v>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529268</v>
+        <v>529301</v>
       </c>
       <c r="R20" t="n">
-        <v>6468138</v>
+        <v>6468100</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121247028</v>
+        <v>121246752</v>
       </c>
       <c r="B21" t="n">
-        <v>105186</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,25 +2749,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529549</v>
+        <v>529338</v>
       </c>
       <c r="R21" t="n">
-        <v>6468258</v>
+        <v>6468183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98842754</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246860</v>
+        <v>121246719</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,32 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529305</v>
+        <v>529388</v>
       </c>
       <c r="R3" t="n">
-        <v>6468117</v>
+        <v>6468198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246857</v>
+        <v>121246744</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>4772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,31 +905,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529305</v>
+        <v>529315</v>
       </c>
       <c r="R4" t="n">
-        <v>6468117</v>
+        <v>6468237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246702</v>
+        <v>121247028</v>
       </c>
       <c r="B6" t="n">
-        <v>91981</v>
+        <v>105200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,26 +1133,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529395</v>
+        <v>529549</v>
       </c>
       <c r="R6" t="n">
-        <v>6468217</v>
+        <v>6468258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246734</v>
+        <v>121246871</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,31 +1236,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1263,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529401</v>
+        <v>529291</v>
       </c>
       <c r="R7" t="n">
-        <v>6468182</v>
+        <v>6468142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246801</v>
+        <v>121246752</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529332</v>
+        <v>529338</v>
       </c>
       <c r="R8" t="n">
-        <v>6468127</v>
+        <v>6468183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246387</v>
+        <v>121246884</v>
       </c>
       <c r="B9" t="n">
-        <v>91987</v>
+        <v>4772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,38 +1451,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529285</v>
+        <v>529268</v>
       </c>
       <c r="R9" t="n">
-        <v>6468189</v>
+        <v>6468138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246884</v>
+        <v>121246860</v>
       </c>
       <c r="B10" t="n">
         <v>4772</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529268</v>
+        <v>529305</v>
       </c>
       <c r="R10" t="n">
-        <v>6468138</v>
+        <v>6468117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246866</v>
+        <v>121246864</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,31 +1667,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,7 +1700,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529289</v>
+        <v>529301</v>
       </c>
       <c r="R11" t="n">
         <v>6468100</v>
@@ -1762,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246852</v>
+        <v>121246742</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,31 +1775,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529325</v>
+        <v>529315</v>
       </c>
       <c r="R12" t="n">
-        <v>6468123</v>
+        <v>6468237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246719</v>
+        <v>121246702</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>91982</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,31 +1881,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529388</v>
+        <v>529395</v>
       </c>
       <c r="R13" t="n">
-        <v>6468198</v>
+        <v>6468217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246742</v>
+        <v>121246801</v>
       </c>
       <c r="B14" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,30 +1987,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529315</v>
+        <v>529332</v>
       </c>
       <c r="R14" t="n">
-        <v>6468237</v>
+        <v>6468127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246776</v>
+        <v>121246852</v>
       </c>
       <c r="B15" t="n">
-        <v>4772</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,36 +2094,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2131,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529371</v>
+        <v>529325</v>
       </c>
       <c r="R15" t="n">
-        <v>6468131</v>
+        <v>6468123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246744</v>
+        <v>121246776</v>
       </c>
       <c r="B16" t="n">
         <v>4772</v>
@@ -2243,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529315</v>
+        <v>529371</v>
       </c>
       <c r="R16" t="n">
-        <v>6468237</v>
+        <v>6468131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246871</v>
+        <v>121246387</v>
       </c>
       <c r="B17" t="n">
-        <v>4772</v>
+        <v>91988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,32 +2313,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>788</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2351,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529291</v>
+        <v>529285</v>
       </c>
       <c r="R17" t="n">
-        <v>6468142</v>
+        <v>6468189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246891</v>
+        <v>121246734</v>
       </c>
       <c r="B18" t="n">
-        <v>4772</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,32 +2427,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529249</v>
+        <v>529401</v>
       </c>
       <c r="R18" t="n">
-        <v>6468138</v>
+        <v>6468182</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121247028</v>
+        <v>121246857</v>
       </c>
       <c r="B19" t="n">
-        <v>105199</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,25 +2534,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529549</v>
+        <v>529305</v>
       </c>
       <c r="R19" t="n">
-        <v>6468258</v>
+        <v>6468117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246864</v>
+        <v>121246866</v>
       </c>
       <c r="B20" t="n">
-        <v>4772</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,32 +2641,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,7 +2673,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529301</v>
+        <v>529289</v>
       </c>
       <c r="R20" t="n">
         <v>6468100</v>
@@ -2737,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246752</v>
+        <v>121246891</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>4772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,31 +2748,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529338</v>
+        <v>529249</v>
       </c>
       <c r="R21" t="n">
-        <v>6468183</v>
+        <v>6468138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98842754</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246719</v>
+        <v>121246864</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>4775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +798,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529388</v>
+        <v>529301</v>
       </c>
       <c r="R3" t="n">
-        <v>6468198</v>
+        <v>6468100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246744</v>
+        <v>121246742</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,32 +910,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246700</v>
+        <v>121246857</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,36 +1012,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529395</v>
+        <v>529305</v>
       </c>
       <c r="R5" t="n">
-        <v>6468217</v>
+        <v>6468117</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247028</v>
+        <v>121246884</v>
       </c>
       <c r="B6" t="n">
-        <v>105200</v>
+        <v>4775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,27 +1123,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529549</v>
+        <v>529268</v>
       </c>
       <c r="R6" t="n">
-        <v>6468258</v>
+        <v>6468138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,12 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246871</v>
+        <v>121247028</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>105203</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,28 +1231,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529291</v>
+        <v>529549</v>
       </c>
       <c r="R7" t="n">
-        <v>6468142</v>
+        <v>6468258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246752</v>
+        <v>121246702</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>91985</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,31 +1334,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529338</v>
+        <v>529395</v>
       </c>
       <c r="R8" t="n">
-        <v>6468183</v>
+        <v>6468217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246884</v>
+        <v>121246891</v>
       </c>
       <c r="B9" t="n">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,7 +1473,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529268</v>
+        <v>529249</v>
       </c>
       <c r="R9" t="n">
         <v>6468138</v>
@@ -1547,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246860</v>
+        <v>121246871</v>
       </c>
       <c r="B10" t="n">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529305</v>
+        <v>529291</v>
       </c>
       <c r="R10" t="n">
-        <v>6468117</v>
+        <v>6468142</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246864</v>
+        <v>121246387</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>91991</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,32 +1656,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>788</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529301</v>
+        <v>529285</v>
       </c>
       <c r="R11" t="n">
-        <v>6468100</v>
+        <v>6468189</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246742</v>
+        <v>121246752</v>
       </c>
       <c r="B12" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,30 +1770,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529315</v>
+        <v>529338</v>
       </c>
       <c r="R12" t="n">
-        <v>6468237</v>
+        <v>6468183</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246702</v>
+        <v>121246866</v>
       </c>
       <c r="B13" t="n">
-        <v>91982</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,30 +1877,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529395</v>
+        <v>529289</v>
       </c>
       <c r="R13" t="n">
-        <v>6468217</v>
+        <v>6468100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246801</v>
+        <v>121246860</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>4775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,31 +1984,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529332</v>
+        <v>529305</v>
       </c>
       <c r="R14" t="n">
-        <v>6468127</v>
+        <v>6468117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246852</v>
+        <v>121246719</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529325</v>
+        <v>529388</v>
       </c>
       <c r="R15" t="n">
-        <v>6468123</v>
+        <v>6468198</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246776</v>
+        <v>121246801</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,36 +2199,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2238,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529371</v>
+        <v>529332</v>
       </c>
       <c r="R16" t="n">
-        <v>6468131</v>
+        <v>6468127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246387</v>
+        <v>121246734</v>
       </c>
       <c r="B17" t="n">
-        <v>91988</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,38 +2306,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2352,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529285</v>
+        <v>529401</v>
       </c>
       <c r="R17" t="n">
-        <v>6468189</v>
+        <v>6468182</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246734</v>
+        <v>121246744</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>4775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,31 +2413,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529401</v>
+        <v>529315</v>
       </c>
       <c r="R18" t="n">
-        <v>6468182</v>
+        <v>6468237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246857</v>
+        <v>121246700</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>4775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,31 +2525,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529305</v>
+        <v>529395</v>
       </c>
       <c r="R19" t="n">
-        <v>6468117</v>
+        <v>6468217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246866</v>
+        <v>121246852</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2673,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529289</v>
+        <v>529325</v>
       </c>
       <c r="R20" t="n">
-        <v>6468100</v>
+        <v>6468123</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246891</v>
+        <v>121246776</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,7 +2769,11 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529249</v>
+        <v>529371</v>
       </c>
       <c r="R21" t="n">
-        <v>6468138</v>
+        <v>6468131</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246864</v>
+        <v>121246801</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,32 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529301</v>
+        <v>529332</v>
       </c>
       <c r="R3" t="n">
-        <v>6468100</v>
+        <v>6468127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246742</v>
+        <v>121246864</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>4775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,26 +909,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529315</v>
+        <v>529301</v>
       </c>
       <c r="R4" t="n">
-        <v>6468237</v>
+        <v>6468100</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246857</v>
+        <v>121246387</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>91991</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,31 +1013,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529305</v>
+        <v>529285</v>
       </c>
       <c r="R5" t="n">
-        <v>6468117</v>
+        <v>6468189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246884</v>
+        <v>121246702</v>
       </c>
       <c r="B6" t="n">
-        <v>4775</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,28 +1131,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529268</v>
+        <v>529395</v>
       </c>
       <c r="R6" t="n">
-        <v>6468138</v>
+        <v>6468217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247028</v>
+        <v>121246852</v>
       </c>
       <c r="B7" t="n">
-        <v>105203</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1233,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529549</v>
+        <v>529325</v>
       </c>
       <c r="R7" t="n">
-        <v>6468258</v>
+        <v>6468123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,12 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246702</v>
+        <v>121246734</v>
       </c>
       <c r="B8" t="n">
-        <v>91985</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,30 +1340,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1365,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529395</v>
+        <v>529401</v>
       </c>
       <c r="R8" t="n">
-        <v>6468217</v>
+        <v>6468182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246891</v>
+        <v>121246857</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,32 +1447,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529249</v>
+        <v>529305</v>
       </c>
       <c r="R9" t="n">
-        <v>6468138</v>
+        <v>6468117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246871</v>
+        <v>121246891</v>
       </c>
       <c r="B10" t="n">
         <v>4775</v>
@@ -1581,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529291</v>
+        <v>529249</v>
       </c>
       <c r="R10" t="n">
-        <v>6468142</v>
+        <v>6468138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246387</v>
+        <v>121246700</v>
       </c>
       <c r="B11" t="n">
-        <v>91991</v>
+        <v>4775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,38 +1662,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1695,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529285</v>
+        <v>529395</v>
       </c>
       <c r="R11" t="n">
-        <v>6468189</v>
+        <v>6468217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246752</v>
+        <v>121246884</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>4775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,31 +1774,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529338</v>
+        <v>529268</v>
       </c>
       <c r="R12" t="n">
-        <v>6468183</v>
+        <v>6468138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246866</v>
+        <v>121246776</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>4775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,31 +1882,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1909,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529289</v>
+        <v>529371</v>
       </c>
       <c r="R13" t="n">
-        <v>6468100</v>
+        <v>6468131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246860</v>
+        <v>121246866</v>
       </c>
       <c r="B14" t="n">
-        <v>4775</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,32 +1994,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2017,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529305</v>
+        <v>529289</v>
       </c>
       <c r="R14" t="n">
-        <v>6468117</v>
+        <v>6468100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246719</v>
+        <v>121246742</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,31 +2101,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2124,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529388</v>
+        <v>529315</v>
       </c>
       <c r="R15" t="n">
-        <v>6468198</v>
+        <v>6468237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246801</v>
+        <v>121247028</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>105203</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,25 +2207,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529332</v>
+        <v>529549</v>
       </c>
       <c r="R16" t="n">
-        <v>6468127</v>
+        <v>6468258</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,12 +2269,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246734</v>
+        <v>121246860</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>4775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,31 +2314,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2338,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529401</v>
+        <v>529305</v>
       </c>
       <c r="R17" t="n">
-        <v>6468182</v>
+        <v>6468117</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246744</v>
+        <v>121246752</v>
       </c>
       <c r="B18" t="n">
-        <v>4775</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,36 +2422,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2450,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529315</v>
+        <v>529338</v>
       </c>
       <c r="R18" t="n">
-        <v>6468237</v>
+        <v>6468183</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246700</v>
+        <v>121246871</v>
       </c>
       <c r="B19" t="n">
         <v>4775</v>
@@ -2550,11 +2554,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529395</v>
+        <v>529291</v>
       </c>
       <c r="R19" t="n">
-        <v>6468217</v>
+        <v>6468142</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246852</v>
+        <v>121246719</v>
       </c>
       <c r="B20" t="n">
         <v>98098</v>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529325</v>
+        <v>529388</v>
       </c>
       <c r="R20" t="n">
-        <v>6468123</v>
+        <v>6468198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246776</v>
+        <v>121246744</v>
       </c>
       <c r="B21" t="n">
         <v>4775</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529371</v>
+        <v>529315</v>
       </c>
       <c r="R21" t="n">
-        <v>6468131</v>
+        <v>6468237</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2842,6 +2842,127 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121549591</v>
+      </c>
+      <c r="B22" t="n">
+        <v>89765</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sankesund, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>529359</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6468164</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Under ved på marken</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98842754</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246801</v>
+        <v>121246871</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>4775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +798,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529332</v>
+        <v>529291</v>
       </c>
       <c r="R3" t="n">
-        <v>6468127</v>
+        <v>6468142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246864</v>
+        <v>121246891</v>
       </c>
       <c r="B4" t="n">
         <v>4775</v>
@@ -938,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529301</v>
+        <v>529249</v>
       </c>
       <c r="R4" t="n">
-        <v>6468100</v>
+        <v>6468138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246387</v>
+        <v>121246742</v>
       </c>
       <c r="B5" t="n">
-        <v>91991</v>
+        <v>91995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,37 +1014,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529285</v>
+        <v>529315</v>
       </c>
       <c r="R5" t="n">
-        <v>6468189</v>
+        <v>6468237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246702</v>
+        <v>121246744</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>4775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,26 +1124,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529395</v>
+        <v>529315</v>
       </c>
       <c r="R6" t="n">
-        <v>6468217</v>
+        <v>6468237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1223,7 @@
         <v>121246852</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246734</v>
+        <v>121246857</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529401</v>
+        <v>529305</v>
       </c>
       <c r="R8" t="n">
-        <v>6468182</v>
+        <v>6468117</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246857</v>
+        <v>121246801</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529305</v>
+        <v>529332</v>
       </c>
       <c r="R9" t="n">
-        <v>6468117</v>
+        <v>6468127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246891</v>
+        <v>121246734</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,32 +1553,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529249</v>
+        <v>529401</v>
       </c>
       <c r="R10" t="n">
-        <v>6468138</v>
+        <v>6468182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246700</v>
+        <v>121246866</v>
       </c>
       <c r="B11" t="n">
-        <v>4775</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,36 +1660,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529395</v>
+        <v>529289</v>
       </c>
       <c r="R11" t="n">
-        <v>6468217</v>
+        <v>6468100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246884</v>
+        <v>121246864</v>
       </c>
       <c r="B12" t="n">
         <v>4775</v>
@@ -1807,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529268</v>
+        <v>529301</v>
       </c>
       <c r="R12" t="n">
-        <v>6468138</v>
+        <v>6468100</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246776</v>
+        <v>121246700</v>
       </c>
       <c r="B13" t="n">
         <v>4775</v>
@@ -1919,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529371</v>
+        <v>529395</v>
       </c>
       <c r="R13" t="n">
-        <v>6468131</v>
+        <v>6468217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246866</v>
+        <v>121246752</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529289</v>
+        <v>529338</v>
       </c>
       <c r="R14" t="n">
-        <v>6468100</v>
+        <v>6468183</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246742</v>
+        <v>121247028</v>
       </c>
       <c r="B15" t="n">
-        <v>91989</v>
+        <v>105209</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,26 +2098,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2132,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529315</v>
+        <v>529549</v>
       </c>
       <c r="R15" t="n">
-        <v>6468237</v>
+        <v>6468258</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,12 +2156,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121247028</v>
+        <v>121246884</v>
       </c>
       <c r="B16" t="n">
-        <v>105203</v>
+        <v>4775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,27 +2205,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2239,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529549</v>
+        <v>529268</v>
       </c>
       <c r="R16" t="n">
-        <v>6468258</v>
+        <v>6468138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,12 +2264,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246860</v>
+        <v>121246702</v>
       </c>
       <c r="B17" t="n">
-        <v>4775</v>
+        <v>91991</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,28 +2313,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2347,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529305</v>
+        <v>529395</v>
       </c>
       <c r="R17" t="n">
-        <v>6468117</v>
+        <v>6468217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246752</v>
+        <v>121246387</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>91997</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,31 +2415,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529338</v>
+        <v>529285</v>
       </c>
       <c r="R18" t="n">
-        <v>6468183</v>
+        <v>6468189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246871</v>
+        <v>121246860</v>
       </c>
       <c r="B19" t="n">
         <v>4775</v>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529291</v>
+        <v>529305</v>
       </c>
       <c r="R19" t="n">
-        <v>6468142</v>
+        <v>6468117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
         <v>121246719</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246744</v>
+        <v>121246776</v>
       </c>
       <c r="B21" t="n">
         <v>4775</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529315</v>
+        <v>529371</v>
       </c>
       <c r="R21" t="n">
-        <v>6468237</v>
+        <v>6468131</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
         <v>121549591</v>
       </c>
       <c r="B22" t="n">
-        <v>89765</v>
+        <v>89768</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -2403,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246387</v>
+        <v>121246860</v>
       </c>
       <c r="B18" t="n">
-        <v>91997</v>
+        <v>4775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,38 +2415,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529285</v>
+        <v>529305</v>
       </c>
       <c r="R18" t="n">
-        <v>6468189</v>
+        <v>6468117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246860</v>
+        <v>121246719</v>
       </c>
       <c r="B19" t="n">
-        <v>4775</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,32 +2523,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2562,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529305</v>
+        <v>529388</v>
       </c>
       <c r="R19" t="n">
-        <v>6468117</v>
+        <v>6468198</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246719</v>
+        <v>121246387</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>91997</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,31 +2630,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529388</v>
+        <v>529285</v>
       </c>
       <c r="R20" t="n">
-        <v>6468198</v>
+        <v>6468189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98842754</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246871</v>
+        <v>121246884</v>
       </c>
       <c r="B3" t="n">
         <v>4775</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529291</v>
+        <v>529268</v>
       </c>
       <c r="R3" t="n">
-        <v>6468142</v>
+        <v>6468138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246891</v>
+        <v>121246752</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,32 +906,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529249</v>
+        <v>529338</v>
       </c>
       <c r="R4" t="n">
-        <v>6468138</v>
+        <v>6468183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246742</v>
+        <v>121246801</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,30 +1013,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529315</v>
+        <v>529332</v>
       </c>
       <c r="R5" t="n">
-        <v>6468237</v>
+        <v>6468127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246744</v>
+        <v>121246734</v>
       </c>
       <c r="B6" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,36 +1120,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529315</v>
+        <v>529401</v>
       </c>
       <c r="R6" t="n">
-        <v>6468237</v>
+        <v>6468182</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246852</v>
+        <v>121246700</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>4775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,31 +1227,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529325</v>
+        <v>529395</v>
       </c>
       <c r="R7" t="n">
-        <v>6468123</v>
+        <v>6468217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246857</v>
+        <v>121247028</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>105210</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529305</v>
+        <v>529549</v>
       </c>
       <c r="R8" t="n">
-        <v>6468117</v>
+        <v>6468258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246801</v>
+        <v>121246744</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>4775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,31 +1446,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529332</v>
+        <v>529315</v>
       </c>
       <c r="R9" t="n">
-        <v>6468127</v>
+        <v>6468237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246734</v>
+        <v>121246860</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>4775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,31 +1558,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1585,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529401</v>
+        <v>529305</v>
       </c>
       <c r="R10" t="n">
-        <v>6468182</v>
+        <v>6468117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246866</v>
+        <v>121246864</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>4775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,31 +1666,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1692,7 +1699,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529289</v>
+        <v>529301</v>
       </c>
       <c r="R11" t="n">
         <v>6468100</v>
@@ -1755,7 +1762,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246864</v>
+        <v>121246776</v>
       </c>
       <c r="B12" t="n">
         <v>4775</v>
@@ -1792,7 +1799,11 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1800,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529301</v>
+        <v>529371</v>
       </c>
       <c r="R12" t="n">
-        <v>6468100</v>
+        <v>6468131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1874,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246700</v>
+        <v>121246871</v>
       </c>
       <c r="B13" t="n">
         <v>4775</v>
@@ -1900,11 +1911,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529395</v>
+        <v>529291</v>
       </c>
       <c r="R13" t="n">
-        <v>6468217</v>
+        <v>6468142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246752</v>
+        <v>121246387</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>91998</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,31 +1994,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529338</v>
+        <v>529285</v>
       </c>
       <c r="R14" t="n">
-        <v>6468183</v>
+        <v>6468189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121247028</v>
+        <v>121246857</v>
       </c>
       <c r="B15" t="n">
-        <v>105209</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,25 +2108,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529549</v>
+        <v>529305</v>
       </c>
       <c r="R15" t="n">
-        <v>6468258</v>
+        <v>6468117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,12 +2170,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246884</v>
+        <v>121246852</v>
       </c>
       <c r="B16" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,32 +2215,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529268</v>
+        <v>529325</v>
       </c>
       <c r="R16" t="n">
-        <v>6468138</v>
+        <v>6468123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,7 +2313,7 @@
         <v>121246702</v>
       </c>
       <c r="B17" t="n">
-        <v>91991</v>
+        <v>91992</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,10 +2416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246860</v>
+        <v>121246719</v>
       </c>
       <c r="B18" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,32 +2428,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529305</v>
+        <v>529388</v>
       </c>
       <c r="R18" t="n">
-        <v>6468117</v>
+        <v>6468198</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246719</v>
+        <v>121246742</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>91996</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,31 +2535,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2555,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529388</v>
+        <v>529315</v>
       </c>
       <c r="R19" t="n">
-        <v>6468198</v>
+        <v>6468237</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246387</v>
+        <v>121246891</v>
       </c>
       <c r="B20" t="n">
-        <v>91997</v>
+        <v>4775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,38 +2641,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>788</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2669,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529285</v>
+        <v>529249</v>
       </c>
       <c r="R20" t="n">
-        <v>6468189</v>
+        <v>6468138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246776</v>
+        <v>121246866</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,36 +2749,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529371</v>
+        <v>529289</v>
       </c>
       <c r="R21" t="n">
-        <v>6468131</v>
+        <v>6468100</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
         <v>121549591</v>
       </c>
       <c r="B22" t="n">
-        <v>89768</v>
+        <v>89769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246884</v>
+        <v>121246776</v>
       </c>
       <c r="B3" t="n">
         <v>4775</v>
@@ -823,7 +823,11 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529268</v>
+        <v>529371</v>
       </c>
       <c r="R3" t="n">
-        <v>6468138</v>
+        <v>6468131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246752</v>
+        <v>121246742</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,31 +910,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529338</v>
+        <v>529315</v>
       </c>
       <c r="R4" t="n">
-        <v>6468183</v>
+        <v>6468237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1215,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246700</v>
+        <v>121246744</v>
       </c>
       <c r="B7" t="n">
         <v>4775</v>
@@ -1264,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529395</v>
+        <v>529315</v>
       </c>
       <c r="R7" t="n">
-        <v>6468217</v>
+        <v>6468237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247028</v>
+        <v>121246387</v>
       </c>
       <c r="B8" t="n">
-        <v>105210</v>
+        <v>91998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,31 +1342,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1371,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529549</v>
+        <v>529285</v>
       </c>
       <c r="R8" t="n">
-        <v>6468258</v>
+        <v>6468189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246744</v>
+        <v>121246852</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,36 +1456,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529315</v>
+        <v>529325</v>
       </c>
       <c r="R9" t="n">
-        <v>6468237</v>
+        <v>6468123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,7 +1659,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246864</v>
+        <v>121246891</v>
       </c>
       <c r="B11" t="n">
         <v>4775</v>
@@ -1699,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529301</v>
+        <v>529249</v>
       </c>
       <c r="R11" t="n">
-        <v>6468100</v>
+        <v>6468138</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,7 +1767,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246776</v>
+        <v>121246864</v>
       </c>
       <c r="B12" t="n">
         <v>4775</v>
@@ -1799,11 +1804,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529371</v>
+        <v>529301</v>
       </c>
       <c r="R12" t="n">
-        <v>6468131</v>
+        <v>6468100</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246871</v>
+        <v>121246702</v>
       </c>
       <c r="B13" t="n">
-        <v>4775</v>
+        <v>91992</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,28 +1891,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>4363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1919,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529291</v>
+        <v>529395</v>
       </c>
       <c r="R13" t="n">
-        <v>6468142</v>
+        <v>6468217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246387</v>
+        <v>121246866</v>
       </c>
       <c r="B14" t="n">
-        <v>91998</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,38 +1993,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2033,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529285</v>
+        <v>529289</v>
       </c>
       <c r="R14" t="n">
-        <v>6468189</v>
+        <v>6468100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246857</v>
+        <v>121246700</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,31 +2100,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529305</v>
+        <v>529395</v>
       </c>
       <c r="R15" t="n">
-        <v>6468117</v>
+        <v>6468217</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246852</v>
+        <v>121246884</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,31 +2212,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2247,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529325</v>
+        <v>529268</v>
       </c>
       <c r="R16" t="n">
-        <v>6468123</v>
+        <v>6468138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246702</v>
+        <v>121246752</v>
       </c>
       <c r="B17" t="n">
-        <v>91992</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,30 +2320,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2353,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529395</v>
+        <v>529338</v>
       </c>
       <c r="R17" t="n">
-        <v>6468217</v>
+        <v>6468183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246719</v>
+        <v>121247028</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>105210</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,25 +2427,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2460,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529388</v>
+        <v>529549</v>
       </c>
       <c r="R18" t="n">
-        <v>6468198</v>
+        <v>6468258</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,12 +2489,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246742</v>
+        <v>121246857</v>
       </c>
       <c r="B19" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,30 +2534,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529315</v>
+        <v>529305</v>
       </c>
       <c r="R19" t="n">
-        <v>6468237</v>
+        <v>6468117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246891</v>
+        <v>121246871</v>
       </c>
       <c r="B20" t="n">
         <v>4775</v>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529249</v>
+        <v>529291</v>
       </c>
       <c r="R20" t="n">
-        <v>6468138</v>
+        <v>6468142</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246866</v>
+        <v>121246719</v>
       </c>
       <c r="B21" t="n">
         <v>98105</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529289</v>
+        <v>529388</v>
       </c>
       <c r="R21" t="n">
-        <v>6468100</v>
+        <v>6468198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246776</v>
+        <v>121246864</v>
       </c>
       <c r="B3" t="n">
         <v>4775</v>
@@ -823,11 +823,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529371</v>
+        <v>529301</v>
       </c>
       <c r="R3" t="n">
-        <v>6468131</v>
+        <v>6468100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246742</v>
+        <v>121246852</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,30 +906,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529315</v>
+        <v>529325</v>
       </c>
       <c r="R4" t="n">
-        <v>6468237</v>
+        <v>6468123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246801</v>
+        <v>121246884</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,31 +1013,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529332</v>
+        <v>529268</v>
       </c>
       <c r="R5" t="n">
-        <v>6468127</v>
+        <v>6468138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246734</v>
+        <v>121246702</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>91992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,31 +1121,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529401</v>
+        <v>529395</v>
       </c>
       <c r="R6" t="n">
-        <v>6468182</v>
+        <v>6468217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246744</v>
+        <v>121246734</v>
       </c>
       <c r="B7" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,36 +1227,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529315</v>
+        <v>529401</v>
       </c>
       <c r="R7" t="n">
-        <v>6468237</v>
+        <v>6468182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121246387</v>
+        <v>121247028</v>
       </c>
       <c r="B8" t="n">
-        <v>91998</v>
+        <v>105210</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,38 +1334,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529285</v>
+        <v>529549</v>
       </c>
       <c r="R8" t="n">
-        <v>6468189</v>
+        <v>6468258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,12 +1396,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246852</v>
+        <v>121246776</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,31 +1441,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1488,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529325</v>
+        <v>529371</v>
       </c>
       <c r="R9" t="n">
-        <v>6468123</v>
+        <v>6468131</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246860</v>
+        <v>121246857</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,32 +1553,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1659,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246891</v>
+        <v>121246752</v>
       </c>
       <c r="B11" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,32 +1660,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1704,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529249</v>
+        <v>529338</v>
       </c>
       <c r="R11" t="n">
-        <v>6468138</v>
+        <v>6468183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246864</v>
+        <v>121246860</v>
       </c>
       <c r="B12" t="n">
         <v>4775</v>
@@ -1812,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529301</v>
+        <v>529305</v>
       </c>
       <c r="R12" t="n">
-        <v>6468100</v>
+        <v>6468117</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246702</v>
+        <v>121246744</v>
       </c>
       <c r="B13" t="n">
-        <v>91992</v>
+        <v>4775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,26 +1879,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1918,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529395</v>
+        <v>529315</v>
       </c>
       <c r="R13" t="n">
-        <v>6468217</v>
+        <v>6468237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246866</v>
+        <v>121246387</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>91998</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,31 +1987,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2025,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529289</v>
+        <v>529285</v>
       </c>
       <c r="R14" t="n">
-        <v>6468100</v>
+        <v>6468189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2088,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246700</v>
+        <v>121246801</v>
       </c>
       <c r="B15" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,36 +2101,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529395</v>
+        <v>529332</v>
       </c>
       <c r="R15" t="n">
-        <v>6468217</v>
+        <v>6468127</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246884</v>
+        <v>121246866</v>
       </c>
       <c r="B16" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,32 +2208,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529268</v>
+        <v>529289</v>
       </c>
       <c r="R16" t="n">
-        <v>6468138</v>
+        <v>6468100</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246752</v>
+        <v>121246871</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,31 +2315,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2352,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529338</v>
+        <v>529291</v>
       </c>
       <c r="R17" t="n">
-        <v>6468183</v>
+        <v>6468142</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121247028</v>
+        <v>121246742</v>
       </c>
       <c r="B18" t="n">
-        <v>105210</v>
+        <v>91996</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,27 +2427,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529549</v>
+        <v>529315</v>
       </c>
       <c r="R18" t="n">
-        <v>6468258</v>
+        <v>6468237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,12 +2484,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246857</v>
+        <v>121246891</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,31 +2529,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2566,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529305</v>
+        <v>529249</v>
       </c>
       <c r="R19" t="n">
-        <v>6468117</v>
+        <v>6468138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246871</v>
+        <v>121246719</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,32 +2637,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529291</v>
+        <v>529388</v>
       </c>
       <c r="R20" t="n">
-        <v>6468142</v>
+        <v>6468198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246719</v>
+        <v>121246700</v>
       </c>
       <c r="B21" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,31 +2744,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529388</v>
+        <v>529395</v>
       </c>
       <c r="R21" t="n">
-        <v>6468198</v>
+        <v>6468217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 10541-2020 artfynd.xlsx
+++ b/artfynd/A 10541-2020 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246852</v>
+        <v>121246387</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>91998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,31 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529325</v>
+        <v>529285</v>
       </c>
       <c r="R4" t="n">
-        <v>6468123</v>
+        <v>6468189</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121246884</v>
+        <v>121246742</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,28 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529268</v>
+        <v>529315</v>
       </c>
       <c r="R5" t="n">
-        <v>6468138</v>
+        <v>6468237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121246702</v>
+        <v>121246719</v>
       </c>
       <c r="B6" t="n">
-        <v>91992</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,30 +1126,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529395</v>
+        <v>529388</v>
       </c>
       <c r="R6" t="n">
-        <v>6468217</v>
+        <v>6468198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121246734</v>
+        <v>121246871</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,31 +1233,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529401</v>
+        <v>529291</v>
       </c>
       <c r="R7" t="n">
-        <v>6468182</v>
+        <v>6468142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247028</v>
+        <v>121246734</v>
       </c>
       <c r="B8" t="n">
-        <v>105210</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,25 +1341,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529549</v>
+        <v>529401</v>
       </c>
       <c r="R8" t="n">
-        <v>6468258</v>
+        <v>6468182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121246776</v>
+        <v>121246700</v>
       </c>
       <c r="B9" t="n">
         <v>4775</v>
@@ -1478,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529371</v>
+        <v>529395</v>
       </c>
       <c r="R9" t="n">
-        <v>6468131</v>
+        <v>6468217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1548,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121246857</v>
+        <v>121246752</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1585,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529305</v>
+        <v>529338</v>
       </c>
       <c r="R10" t="n">
-        <v>6468117</v>
+        <v>6468183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,7 +1655,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121246752</v>
+        <v>121246801</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1692,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529338</v>
+        <v>529332</v>
       </c>
       <c r="R11" t="n">
-        <v>6468183</v>
+        <v>6468127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121246860</v>
+        <v>121246852</v>
       </c>
       <c r="B12" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,32 +1774,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1800,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529305</v>
+        <v>529325</v>
       </c>
       <c r="R12" t="n">
-        <v>6468117</v>
+        <v>6468123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121246744</v>
+        <v>121247028</v>
       </c>
       <c r="B13" t="n">
-        <v>4775</v>
+        <v>105210</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,32 +1885,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529315</v>
+        <v>529549</v>
       </c>
       <c r="R13" t="n">
-        <v>6468237</v>
+        <v>6468258</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,12 +1943,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121246387</v>
+        <v>121246702</v>
       </c>
       <c r="B14" t="n">
-        <v>91998</v>
+        <v>91992</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,37 +1988,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>4363</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2026,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529285</v>
+        <v>529395</v>
       </c>
       <c r="R14" t="n">
-        <v>6468189</v>
+        <v>6468217</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121246801</v>
+        <v>121246776</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,31 +2094,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529332</v>
+        <v>529371</v>
       </c>
       <c r="R15" t="n">
-        <v>6468127</v>
+        <v>6468131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246866</v>
+        <v>121246891</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,31 +2206,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2240,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529289</v>
+        <v>529249</v>
       </c>
       <c r="R16" t="n">
-        <v>6468100</v>
+        <v>6468138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121246871</v>
+        <v>121246857</v>
       </c>
       <c r="B17" t="n">
-        <v>4775</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,32 +2314,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2348,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529291</v>
+        <v>529305</v>
       </c>
       <c r="R17" t="n">
-        <v>6468142</v>
+        <v>6468117</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121246742</v>
+        <v>121246866</v>
       </c>
       <c r="B18" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,30 +2421,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529315</v>
+        <v>529289</v>
       </c>
       <c r="R18" t="n">
-        <v>6468237</v>
+        <v>6468100</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2516,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246891</v>
+        <v>121246860</v>
       </c>
       <c r="B19" t="n">
         <v>4775</v>
@@ -2562,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529249</v>
+        <v>529305</v>
       </c>
       <c r="R19" t="n">
-        <v>6468138</v>
+        <v>6468117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121246719</v>
+        <v>121246884</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,31 +2636,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529388</v>
+        <v>529268</v>
       </c>
       <c r="R20" t="n">
-        <v>6468198</v>
+        <v>6468138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121246700</v>
+        <v>121246744</v>
       </c>
       <c r="B21" t="n">
         <v>4775</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529395</v>
+        <v>529315</v>
       </c>
       <c r="R21" t="n">
-        <v>6468217</v>
+        <v>6468237</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
